--- a/artfynd/A 4828-2023 artfynd.xlsx
+++ b/artfynd/A 4828-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4828-2023 artfynd.xlsx
+++ b/artfynd/A 4828-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111145172</v>
+        <v>111145180</v>
       </c>
       <c r="B2" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568420.8942379961</v>
+        <v>568421</v>
       </c>
       <c r="R2" t="n">
-        <v>7144652.686749269</v>
+        <v>7144653</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -749,19 +744,9 @@
           <t>2023-07-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,12 +776,7 @@
         <v>111145167</v>
       </c>
       <c r="B3" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568420.8942379961</v>
+        <v>568421</v>
       </c>
       <c r="R3" t="n">
-        <v>7144652.686749269</v>
+        <v>7144653</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,19 +842,9 @@
           <t>2023-07-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,37 +871,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111145170</v>
+        <v>111145172</v>
       </c>
       <c r="B4" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568420.8942379961</v>
+        <v>568421</v>
       </c>
       <c r="R4" t="n">
-        <v>7144652.686749269</v>
+        <v>7144653</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -975,19 +940,9 @@
           <t>2023-07-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,119 +966,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>111145180</v>
-      </c>
-      <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Fjälltuna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>568420.8942379961</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7144652.686749269</v>
-      </c>
-      <c r="S5" t="n">
-        <v>20</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4828-2023 artfynd.xlsx
+++ b/artfynd/A 4828-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111145180</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111145167</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,8 +981,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111145172</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>